--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/75.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/75.xlsx
@@ -426,13 +426,13 @@
         <v>-0.8508845205317002</v>
       </c>
       <c r="E2">
-        <v>-7.892104308477294</v>
+        <v>-0.7500758689680816</v>
       </c>
       <c r="F2">
-        <v>-4.0634727765728</v>
+        <v>-2.854574926479674</v>
       </c>
       <c r="G2">
-        <v>-10.43080207637654</v>
+        <v>-7.632366332302283</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-0.3987269486885421</v>
       </c>
       <c r="E3">
-        <v>-7.632740488161982</v>
+        <v>-2.222916755222789</v>
       </c>
       <c r="F3">
-        <v>-3.736397706149234</v>
+        <v>-2.512344046054489</v>
       </c>
       <c r="G3">
-        <v>-10.53495789233799</v>
+        <v>-7.581349899496037</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-0.1033608283904744</v>
       </c>
       <c r="E4">
-        <v>-8.414531712372185</v>
+        <v>-2.851976136576293</v>
       </c>
       <c r="F4">
-        <v>-3.976462721317545</v>
+        <v>-2.394796226495031</v>
       </c>
       <c r="G4">
-        <v>-10.97292222120644</v>
+        <v>-6.990405177861603</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-0.01824558530853979</v>
       </c>
       <c r="E5">
-        <v>-8.824761644253035</v>
+        <v>-3.46812483853393</v>
       </c>
       <c r="F5">
-        <v>-3.980840643041341</v>
+        <v>-2.739378841976764</v>
       </c>
       <c r="G5">
-        <v>-10.5608073557833</v>
+        <v>-6.921811241161411</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-0.09782562648099007</v>
       </c>
       <c r="E6">
-        <v>-9.59577962879899</v>
+        <v>-3.802226593871834</v>
       </c>
       <c r="F6">
-        <v>-3.606946247011547</v>
+        <v>-2.585337296486973</v>
       </c>
       <c r="G6">
-        <v>-10.61377283419586</v>
+        <v>-6.828821422166748</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-0.3059437458264935</v>
       </c>
       <c r="E7">
-        <v>-10.12390838146954</v>
+        <v>-4.928295054515175</v>
       </c>
       <c r="F7">
-        <v>-3.722453797657911</v>
+        <v>-2.314992967644132</v>
       </c>
       <c r="G7">
-        <v>-10.87082373116276</v>
+        <v>-6.199817811664315</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-0.5847057794510034</v>
       </c>
       <c r="E8">
-        <v>-10.32134531972996</v>
+        <v>-5.72695484440395</v>
       </c>
       <c r="F8">
-        <v>-3.768239320745445</v>
+        <v>-1.944772381045755</v>
       </c>
       <c r="G8">
-        <v>-10.86761797769918</v>
+        <v>-7.03993849852298</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-0.8766525943454755</v>
       </c>
       <c r="E9">
-        <v>-11.85355902869923</v>
+        <v>-6.122240812059488</v>
       </c>
       <c r="F9">
-        <v>-3.389300995600006</v>
+        <v>-1.999421435343244</v>
       </c>
       <c r="G9">
-        <v>-10.81087253205014</v>
+        <v>-7.080012057428479</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-1.118206965293871</v>
       </c>
       <c r="E10">
-        <v>-11.70341294450091</v>
+        <v>-6.910462469360583</v>
       </c>
       <c r="F10">
-        <v>-3.405932956313414</v>
+        <v>-2.070878064243534</v>
       </c>
       <c r="G10">
-        <v>-10.51350854700391</v>
+        <v>-6.194574419612322</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-1.255661545865365</v>
       </c>
       <c r="E11">
-        <v>-11.49971312668788</v>
+        <v>-7.41060072418972</v>
       </c>
       <c r="F11">
-        <v>-3.300568764514331</v>
+        <v>-1.822499553820728</v>
       </c>
       <c r="G11">
-        <v>-9.756740731419812</v>
+        <v>-5.75524838379671</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-1.248023795430657</v>
       </c>
       <c r="E12">
-        <v>-12.90111280699758</v>
+        <v>-8.074868990952861</v>
       </c>
       <c r="F12">
-        <v>-3.088482686742976</v>
+        <v>-1.947721368999721</v>
       </c>
       <c r="G12">
-        <v>-9.293373185238149</v>
+        <v>-5.094735202658929</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-1.07774644060854</v>
       </c>
       <c r="E13">
-        <v>-13.52146846130835</v>
+        <v>-9.14991966342579</v>
       </c>
       <c r="F13">
-        <v>-2.790924831983366</v>
+        <v>-1.200261438799046</v>
       </c>
       <c r="G13">
-        <v>-9.015785122530685</v>
+        <v>-5.392561839945047</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-0.7510303220049577</v>
       </c>
       <c r="E14">
-        <v>-14.14750282202473</v>
+        <v>-9.534405220573033</v>
       </c>
       <c r="F14">
-        <v>-2.825731173514195</v>
+        <v>-1.264366306999491</v>
       </c>
       <c r="G14">
-        <v>-9.124518242567564</v>
+        <v>-4.448593771951516</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-0.299713071676901</v>
       </c>
       <c r="E15">
-        <v>-14.83276962276144</v>
+        <v>-10.81293834410662</v>
       </c>
       <c r="F15">
-        <v>-2.465132902666737</v>
+        <v>-0.5277248550793776</v>
       </c>
       <c r="G15">
-        <v>-7.783945643462391</v>
+        <v>-5.092641783304003</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>0.2239646579434012</v>
       </c>
       <c r="E16">
-        <v>-15.51465818188842</v>
+        <v>-9.733196172561748</v>
       </c>
       <c r="F16">
-        <v>-2.240185592599517</v>
+        <v>-0.8888300867773493</v>
       </c>
       <c r="G16">
-        <v>-7.84375246882639</v>
+        <v>-4.443478347540342</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>0.7566063875088628</v>
       </c>
       <c r="E17">
-        <v>-16.28538634409789</v>
+        <v>-11.68467864753118</v>
       </c>
       <c r="F17">
-        <v>-2.114843664147118</v>
+        <v>-0.07415228367650829</v>
       </c>
       <c r="G17">
-        <v>-7.32328182384571</v>
+        <v>-3.435008026131246</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>1.235182606600105</v>
       </c>
       <c r="E18">
-        <v>-17.23571378545156</v>
+        <v>-13.75862464509004</v>
       </c>
       <c r="F18">
-        <v>-1.67293864761268</v>
+        <v>0.02862905856064596</v>
       </c>
       <c r="G18">
-        <v>-7.679556860770217</v>
+        <v>-4.051595494252741</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>1.607108459066251</v>
       </c>
       <c r="E19">
-        <v>-17.59290170128056</v>
+        <v>-14.36090715963619</v>
       </c>
       <c r="F19">
-        <v>-1.264116140043846</v>
+        <v>0.2103099108122447</v>
       </c>
       <c r="G19">
-        <v>-6.824030838689959</v>
+        <v>-2.327996058848907</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>1.839075493761127</v>
       </c>
       <c r="E20">
-        <v>-18.34751302449673</v>
+        <v>-14.78981704679868</v>
       </c>
       <c r="F20">
-        <v>-0.8330652215882893</v>
+        <v>0.7796302594082889</v>
       </c>
       <c r="G20">
-        <v>-6.251503613668688</v>
+        <v>-2.076716830605071</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>1.920958664134669</v>
       </c>
       <c r="E21">
-        <v>-19.51263504498222</v>
+        <v>-15.28381921934743</v>
       </c>
       <c r="F21">
-        <v>-0.5915828697937887</v>
+        <v>0.7027652197351201</v>
       </c>
       <c r="G21">
-        <v>-6.381476080859852</v>
+        <v>-2.429398929921986</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>1.863088181237729</v>
       </c>
       <c r="E22">
-        <v>-19.52730730076707</v>
+        <v>-14.45935165608894</v>
       </c>
       <c r="F22">
-        <v>-0.6231801160061731</v>
+        <v>0.9179957801675016</v>
       </c>
       <c r="G22">
-        <v>-5.960324731262005</v>
+        <v>-2.077323856593568</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>1.691762958089006</v>
       </c>
       <c r="E23">
-        <v>-20.88049231831711</v>
+        <v>-15.82657041458874</v>
       </c>
       <c r="F23">
-        <v>-0.5013479802394357</v>
+        <v>1.423395986493925</v>
       </c>
       <c r="G23">
-        <v>-6.454361855359798</v>
+        <v>-2.084371920503255</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>1.443093579107769</v>
       </c>
       <c r="E24">
-        <v>-21.02874550038022</v>
+        <v>-17.58100540006242</v>
       </c>
       <c r="F24">
-        <v>-0.2258884826843078</v>
+        <v>1.061651255160992</v>
       </c>
       <c r="G24">
-        <v>-6.190545079537324</v>
+        <v>-2.009435382528657</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>1.156378736633539</v>
       </c>
       <c r="E25">
-        <v>-21.11651638359688</v>
+        <v>-16.39655585251219</v>
       </c>
       <c r="F25">
-        <v>-0.2118799615355653</v>
+        <v>1.609886339886177</v>
       </c>
       <c r="G25">
-        <v>-6.64781611606154</v>
+        <v>-1.364465347917966</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>0.8655891749979548</v>
       </c>
       <c r="E26">
-        <v>-21.01275093018513</v>
+        <v>-17.06962747274624</v>
       </c>
       <c r="F26">
-        <v>-0.3681580990129144</v>
+        <v>1.983417082626142</v>
       </c>
       <c r="G26">
-        <v>-6.314808221215054</v>
+        <v>-1.748614361989956</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>0.5952956669469337</v>
       </c>
       <c r="E27">
-        <v>-21.30424880205887</v>
+        <v>-17.35256200027148</v>
       </c>
       <c r="F27">
-        <v>-0.3119376317523148</v>
+        <v>1.397600625570748</v>
       </c>
       <c r="G27">
-        <v>-6.086910977803822</v>
+        <v>-1.979428611367535</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>0.3588227530567381</v>
       </c>
       <c r="E28">
-        <v>-21.54282692667897</v>
+        <v>-17.09217021635642</v>
       </c>
       <c r="F28">
-        <v>-0.3389871409233298</v>
+        <v>1.667514203364133</v>
       </c>
       <c r="G28">
-        <v>-6.39324910381514</v>
+        <v>-2.963355395511984</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>0.1580865659515967</v>
       </c>
       <c r="E29">
-        <v>-20.67421127031971</v>
+        <v>-16.652084055343</v>
       </c>
       <c r="F29">
-        <v>-0.1846589803121707</v>
+        <v>1.145616231843555</v>
       </c>
       <c r="G29">
-        <v>-6.439855574845493</v>
+        <v>-3.053464301977455</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.01421947343651319</v>
       </c>
       <c r="E30">
-        <v>-20.4958527930536</v>
+        <v>-16.45307120812791</v>
       </c>
       <c r="F30">
-        <v>-0.2710510734849368</v>
+        <v>1.178580284270559</v>
       </c>
       <c r="G30">
-        <v>-6.431393304443685</v>
+        <v>-2.185545106067174</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.1712129050040516</v>
       </c>
       <c r="E31">
-        <v>-20.77405506524082</v>
+        <v>-16.78871264462843</v>
       </c>
       <c r="F31">
-        <v>0.04639422588108416</v>
+        <v>1.16673297367572</v>
       </c>
       <c r="G31">
-        <v>-6.738997981976949</v>
+        <v>-2.389994740214615</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.3296581869304784</v>
       </c>
       <c r="E32">
-        <v>-20.13168197030476</v>
+        <v>-15.77739118686544</v>
       </c>
       <c r="F32">
-        <v>-0.4039129212199495</v>
+        <v>1.44698954686046</v>
       </c>
       <c r="G32">
-        <v>-6.414147203927244</v>
+        <v>-2.091295297993684</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-0.5080633203442799</v>
       </c>
       <c r="E33">
-        <v>-19.64411475932092</v>
+        <v>-15.63698585025762</v>
       </c>
       <c r="F33">
-        <v>-0.3747113135364613</v>
+        <v>1.231564320088421</v>
       </c>
       <c r="G33">
-        <v>-6.690547464430188</v>
+        <v>-3.280564208549743</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.7248339701557011</v>
       </c>
       <c r="E34">
-        <v>-19.97749648729161</v>
+        <v>-15.14558755026329</v>
       </c>
       <c r="F34">
-        <v>-0.3811361311125743</v>
+        <v>1.350960227323525</v>
       </c>
       <c r="G34">
-        <v>-6.510204965079987</v>
+        <v>-3.032270891925002</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.9957322933265322</v>
       </c>
       <c r="E35">
-        <v>-19.40689970537712</v>
+        <v>-14.39463523404532</v>
       </c>
       <c r="F35">
-        <v>-0.3495082353062864</v>
+        <v>1.00198892134176</v>
       </c>
       <c r="G35">
-        <v>-6.519310354907446</v>
+        <v>-2.735507370424143</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-1.331372856209262</v>
       </c>
       <c r="E36">
-        <v>-19.22418936458965</v>
+        <v>-14.70039327056922</v>
       </c>
       <c r="F36">
-        <v>-0.215765004654695</v>
+        <v>1.333604273500069</v>
       </c>
       <c r="G36">
-        <v>-6.469393131323614</v>
+        <v>-2.43735261098208</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-1.734780138552403</v>
       </c>
       <c r="E37">
-        <v>-19.01725168786114</v>
+        <v>-15.28800805780452</v>
       </c>
       <c r="F37">
-        <v>-0.2263051514879159</v>
+        <v>1.602596706741542</v>
       </c>
       <c r="G37">
-        <v>-6.182099215243313</v>
+        <v>-2.835299161711535</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.20220122833924</v>
       </c>
       <c r="E38">
-        <v>-19.04454932917938</v>
+        <v>-15.3390077320789</v>
       </c>
       <c r="F38">
-        <v>0.04489819435162825</v>
+        <v>1.117055780529834</v>
       </c>
       <c r="G38">
-        <v>-6.7800624697934</v>
+        <v>-1.902651308098088</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.721955871220562</v>
       </c>
       <c r="E39">
-        <v>-18.38945122228176</v>
+        <v>-13.83248858462915</v>
       </c>
       <c r="F39">
-        <v>-0.07919041422033489</v>
+        <v>1.349141132506977</v>
       </c>
       <c r="G39">
-        <v>-6.2956294812001</v>
+        <v>-1.702933195439367</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.273489064686785</v>
       </c>
       <c r="E40">
-        <v>-17.73572524300848</v>
+        <v>-13.30989815566999</v>
       </c>
       <c r="F40">
-        <v>-0.05676319515694107</v>
+        <v>1.630224416359711</v>
       </c>
       <c r="G40">
-        <v>-6.042322458032528</v>
+        <v>-2.556917043386686</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.829791951160137</v>
       </c>
       <c r="E41">
-        <v>-17.6422167832241</v>
+        <v>-12.90237625124572</v>
       </c>
       <c r="F41">
-        <v>-0.186261042869185</v>
+        <v>1.451891825150228</v>
       </c>
       <c r="G41">
-        <v>-6.146337181466925</v>
+        <v>-2.091301860436803</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.363757337232806</v>
       </c>
       <c r="E42">
-        <v>-16.87656504037723</v>
+        <v>-12.91713454803672</v>
       </c>
       <c r="F42">
-        <v>-0.00742646101360532</v>
+        <v>1.317239047090363</v>
       </c>
       <c r="G42">
-        <v>-6.148492944031481</v>
+        <v>-2.378100312061628</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.850655129531139</v>
       </c>
       <c r="E43">
-        <v>-16.78872623005045</v>
+        <v>-11.5321913422709</v>
       </c>
       <c r="F43">
-        <v>0.001189388342912338</v>
+        <v>1.372027267111522</v>
       </c>
       <c r="G43">
-        <v>-6.420601366734672</v>
+        <v>-2.556014707457839</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.268680235144138</v>
       </c>
       <c r="E44">
-        <v>-16.10630783946456</v>
+        <v>-11.7927325658282</v>
       </c>
       <c r="F44">
-        <v>-0.1624106886077816</v>
+        <v>1.165725678913916</v>
       </c>
       <c r="G44">
-        <v>-6.096869485236737</v>
+        <v>-1.307050533070802</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.601070800435394</v>
       </c>
       <c r="E45">
-        <v>-15.95675498536125</v>
+        <v>-10.89001750019118</v>
       </c>
       <c r="F45">
-        <v>-0.07961536669797104</v>
+        <v>1.442294360421393</v>
       </c>
       <c r="G45">
-        <v>-6.102605060522646</v>
+        <v>-1.512015319003076</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.840401058684268</v>
       </c>
       <c r="E46">
-        <v>-16.19209525106587</v>
+        <v>-11.92845546031209</v>
       </c>
       <c r="F46">
-        <v>-0.1300256649953349</v>
+        <v>1.242155825700615</v>
       </c>
       <c r="G46">
-        <v>-5.737382132405533</v>
+        <v>-1.074320050302508</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.987107509926664</v>
       </c>
       <c r="E47">
-        <v>-15.50386682832814</v>
+        <v>-11.39860135904462</v>
       </c>
       <c r="F47">
-        <v>-0.09263978737218766</v>
+        <v>1.123629704238451</v>
       </c>
       <c r="G47">
-        <v>-5.56361520106046</v>
+        <v>-1.61498989520313</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.046081161958705</v>
       </c>
       <c r="E48">
-        <v>-15.45886738211392</v>
+        <v>-11.06190931657433</v>
       </c>
       <c r="F48">
-        <v>-0.2160309105909936</v>
+        <v>1.076808721897417</v>
       </c>
       <c r="G48">
-        <v>-5.930944673418736</v>
+        <v>-1.09156286959739</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.027278164475309</v>
       </c>
       <c r="E49">
-        <v>-14.51430015969801</v>
+        <v>-10.81897027148484</v>
       </c>
       <c r="F49">
-        <v>-0.1220857634395017</v>
+        <v>1.232341328712247</v>
       </c>
       <c r="G49">
-        <v>-5.288035245947377</v>
+        <v>-0.8307713800527236</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.94574362655393</v>
       </c>
       <c r="E50">
-        <v>-14.20277284728834</v>
+        <v>-8.78909991144263</v>
       </c>
       <c r="F50">
-        <v>-0.1488967027985105</v>
+        <v>1.052368570045221</v>
       </c>
       <c r="G50">
-        <v>-5.313412213488122</v>
+        <v>-1.42713996092492</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.81789943927419</v>
       </c>
       <c r="E51">
-        <v>-13.96584308720703</v>
+        <v>-8.244229390365726</v>
       </c>
       <c r="F51">
-        <v>-0.4270740738022237</v>
+        <v>1.009846814524716</v>
       </c>
       <c r="G51">
-        <v>-5.751658727410677</v>
+        <v>-1.100231856957443</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.657591344042428</v>
       </c>
       <c r="E52">
-        <v>-13.35177748329292</v>
+        <v>-8.997169706673061</v>
       </c>
       <c r="F52">
-        <v>-0.3933354978536026</v>
+        <v>0.8843226452437016</v>
       </c>
       <c r="G52">
-        <v>-4.820257737989819</v>
+        <v>-0.1201145710435087</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.474333721892377</v>
       </c>
       <c r="E53">
-        <v>-12.84430762904537</v>
+        <v>-8.36454641627552</v>
       </c>
       <c r="F53">
-        <v>-0.3325532113057861</v>
+        <v>1.119428224771452</v>
       </c>
       <c r="G53">
-        <v>-5.644172471566387</v>
+        <v>-0.9004218700950566</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.275396592379612</v>
       </c>
       <c r="E54">
-        <v>-12.65517591211501</v>
+        <v>-7.87710600256389</v>
       </c>
       <c r="F54">
-        <v>-0.1790890378957469</v>
+        <v>0.3012439424545605</v>
       </c>
       <c r="G54">
-        <v>-5.125949463353926</v>
+        <v>-1.120083247392083</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.067601571966618</v>
       </c>
       <c r="E55">
-        <v>-12.01113633874414</v>
+        <v>-7.846389363369862</v>
       </c>
       <c r="F55">
-        <v>-0.2080288814799504</v>
+        <v>0.6774809614994707</v>
       </c>
       <c r="G55">
-        <v>-5.472643333324855</v>
+        <v>-1.597770044459164</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.855320590329153</v>
       </c>
       <c r="E56">
-        <v>-12.27603395429682</v>
+        <v>-6.456881455804305</v>
       </c>
       <c r="F56">
-        <v>-0.3386881002909192</v>
+        <v>0.995308966605585</v>
       </c>
       <c r="G56">
-        <v>-5.402182381557339</v>
+        <v>-1.053874758765608</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.640193674039147</v>
       </c>
       <c r="E57">
-        <v>-11.86879281526103</v>
+        <v>-7.871789574078885</v>
       </c>
       <c r="F57">
-        <v>-0.2014375620558747</v>
+        <v>0.8995447246375454</v>
       </c>
       <c r="G57">
-        <v>-5.989301198853461</v>
+        <v>-1.505013192195221</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.424137421889244</v>
       </c>
       <c r="E58">
-        <v>-11.11719292725997</v>
+        <v>-6.184742810313354</v>
       </c>
       <c r="F58">
-        <v>-0.2940001640120943</v>
+        <v>0.5494476673553763</v>
       </c>
       <c r="G58">
-        <v>-5.907943310287029</v>
+        <v>-1.975507551603999</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.209430262298409</v>
       </c>
       <c r="E59">
-        <v>-11.28448834252534</v>
+        <v>-6.214046565616989</v>
       </c>
       <c r="F59">
-        <v>-0.07890959767078586</v>
+        <v>1.096359849338291</v>
       </c>
       <c r="G59">
-        <v>-6.018858442660939</v>
+        <v>-2.267021118609746</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.995689492619053</v>
       </c>
       <c r="E60">
-        <v>-11.67482468809049</v>
+        <v>-5.662682212813085</v>
       </c>
       <c r="F60">
-        <v>-0.3661675321439872</v>
+        <v>0.981286363210995</v>
       </c>
       <c r="G60">
-        <v>-6.490878570094858</v>
+        <v>-1.760101918669572</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.781373456369487</v>
       </c>
       <c r="E61">
-        <v>-11.31606086330681</v>
+        <v>-5.089323061753926</v>
       </c>
       <c r="F61">
-        <v>0.01775176619448565</v>
+        <v>1.111229044218542</v>
       </c>
       <c r="G61">
-        <v>-6.235136880530177</v>
+        <v>-2.327471063399396</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-3.566812157943454</v>
       </c>
       <c r="E62">
-        <v>-11.52964633987859</v>
+        <v>-6.024638611772168</v>
       </c>
       <c r="F62">
-        <v>-0.1776294545320141</v>
+        <v>1.260424640401956</v>
       </c>
       <c r="G62">
-        <v>-5.912950454386742</v>
+        <v>-2.354577234701968</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-3.35600201448978</v>
       </c>
       <c r="E63">
-        <v>-10.6764274951454</v>
+        <v>-4.099009194912526</v>
       </c>
       <c r="F63">
-        <v>-0.132591118841805</v>
+        <v>1.097502996354154</v>
       </c>
       <c r="G63">
-        <v>-6.58239840183089</v>
+        <v>-2.967050050987919</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-3.153240049488804</v>
       </c>
       <c r="E64">
-        <v>-10.41168384770897</v>
+        <v>-5.5166298691177</v>
       </c>
       <c r="F64">
-        <v>-0.2278384595504978</v>
+        <v>0.6763328442791906</v>
       </c>
       <c r="G64">
-        <v>-6.933344734942859</v>
+        <v>-3.930351076409699</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.962595188396102</v>
       </c>
       <c r="E65">
-        <v>-10.37580021967219</v>
+        <v>-6.111105294474626</v>
       </c>
       <c r="F65">
-        <v>-0.153765846392166</v>
+        <v>0.7908032789372487</v>
       </c>
       <c r="G65">
-        <v>-7.168444259677073</v>
+        <v>-4.178982358855063</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.788727595203409</v>
       </c>
       <c r="E66">
-        <v>-10.01124900510671</v>
+        <v>-5.123440584927714</v>
       </c>
       <c r="F66">
-        <v>-0.08616858122151792</v>
+        <v>0.771775679694944</v>
       </c>
       <c r="G66">
-        <v>-7.033789489320581</v>
+        <v>-3.661858559865016</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.637555483817755</v>
       </c>
       <c r="E67">
-        <v>-9.654038446907668</v>
+        <v>-5.664335105825884</v>
       </c>
       <c r="F67">
-        <v>0.02608348553184308</v>
+        <v>0.8186099159144224</v>
       </c>
       <c r="G67">
-        <v>-7.000508059043133</v>
+        <v>-4.182522796917704</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.512556514506536</v>
       </c>
       <c r="E68">
-        <v>-9.896117081935703</v>
+        <v>-5.303193832188181</v>
       </c>
       <c r="F68">
-        <v>0.02009521757700546</v>
+        <v>0.8464066124827627</v>
       </c>
       <c r="G68">
-        <v>-7.757941962603792</v>
+        <v>-4.209871778615675</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-2.415397794867752</v>
       </c>
       <c r="E69">
-        <v>-10.74931328429885</v>
+        <v>-4.319781359734471</v>
       </c>
       <c r="F69">
-        <v>-0.1650888004210324</v>
+        <v>1.024215675493677</v>
       </c>
       <c r="G69">
-        <v>-6.971607059547544</v>
+        <v>-4.221999173499383</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.346177079428792</v>
       </c>
       <c r="E70">
-        <v>-10.51933473181931</v>
+        <v>-4.975767047537584</v>
       </c>
       <c r="F70">
-        <v>0.05509539708009017</v>
+        <v>0.6069960075626636</v>
       </c>
       <c r="G70">
-        <v>-7.250569954088415</v>
+        <v>-4.029256937876041</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-2.306132073615967</v>
       </c>
       <c r="E71">
-        <v>-10.34632891083027</v>
+        <v>-5.276099972200289</v>
       </c>
       <c r="F71">
-        <v>-0.2081796443472599</v>
+        <v>0.7026161136026161</v>
       </c>
       <c r="G71">
-        <v>-7.693436427966668</v>
+        <v>-4.325794055089298</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-2.29444018597532</v>
       </c>
       <c r="E72">
-        <v>-10.46816297553264</v>
+        <v>-5.769812322412543</v>
       </c>
       <c r="F72">
-        <v>-0.1254423081556453</v>
+        <v>0.3842587817261129</v>
       </c>
       <c r="G72">
-        <v>-7.532128294882806</v>
+        <v>-4.093532787004003</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-2.308575639843153</v>
       </c>
       <c r="E73">
-        <v>-10.93914238622639</v>
+        <v>-5.301572638493435</v>
       </c>
       <c r="F73">
-        <v>-0.3806109461791994</v>
+        <v>0.7578060918141332</v>
       </c>
       <c r="G73">
-        <v>-7.459659235520911</v>
+        <v>-4.606791306997025</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-2.345914402694229</v>
       </c>
       <c r="E74">
-        <v>-10.47556250206117</v>
+        <v>-5.231634885918974</v>
       </c>
       <c r="F74">
-        <v>-0.2370010313928631</v>
+        <v>0.6935280948265027</v>
       </c>
       <c r="G74">
-        <v>-7.251770881179172</v>
+        <v>-3.754799160536288</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-2.406183490379933</v>
       </c>
       <c r="E75">
-        <v>-11.02190477719057</v>
+        <v>-5.279595954134211</v>
       </c>
       <c r="F75">
-        <v>-0.20869157540219</v>
+        <v>0.5772849539264537</v>
       </c>
       <c r="G75">
-        <v>-6.840473039924336</v>
+        <v>-3.706830982558765</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-2.486995454092769</v>
       </c>
       <c r="E76">
-        <v>-11.21288863999006</v>
+        <v>-6.12674664369712</v>
       </c>
       <c r="F76">
-        <v>-0.2100335305947252</v>
+        <v>0.3125975460773305</v>
       </c>
       <c r="G76">
-        <v>-6.80458303850713</v>
+        <v>-3.761565039391863</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-2.584999985650547</v>
       </c>
       <c r="E77">
-        <v>-11.34982063703399</v>
+        <v>-6.077232308897252</v>
       </c>
       <c r="F77">
-        <v>-0.3898124512894963</v>
+        <v>0.8286778933280476</v>
       </c>
       <c r="G77">
-        <v>-6.698737393442562</v>
+        <v>-3.534176385322344</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.69564578370082</v>
       </c>
       <c r="E78">
-        <v>-11.6791991939819</v>
+        <v>-6.826332479246083</v>
       </c>
       <c r="F78">
-        <v>-0.4122893723970581</v>
+        <v>0.3259723661629313</v>
       </c>
       <c r="G78">
-        <v>-6.517705837564878</v>
+        <v>-3.481512779293256</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.815748349861157</v>
       </c>
       <c r="E79">
-        <v>-12.39441279333133</v>
+        <v>-7.957785295484545</v>
       </c>
       <c r="F79">
-        <v>-0.5280760828581645</v>
+        <v>0.2432474554823587</v>
       </c>
       <c r="G79">
-        <v>-6.595060635828787</v>
+        <v>-4.005372926144843</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.940955067349593</v>
       </c>
       <c r="E80">
-        <v>-13.55838910989288</v>
+        <v>-8.018865352900002</v>
       </c>
       <c r="F80">
-        <v>-0.5729727677224949</v>
+        <v>0.504902210269833</v>
       </c>
       <c r="G80">
-        <v>-6.292538570491104</v>
+        <v>-3.567018131910826</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.067742854704627</v>
       </c>
       <c r="E81">
-        <v>-13.07539112918278</v>
+        <v>-8.901111716022356</v>
       </c>
       <c r="F81">
-        <v>-0.5959922694788905</v>
+        <v>-0.08284102936447231</v>
       </c>
       <c r="G81">
-        <v>-6.208467111695011</v>
+        <v>-3.698171838863391</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.193324046511632</v>
       </c>
       <c r="E82">
-        <v>-14.00391849666352</v>
+        <v>-9.019889060769543</v>
       </c>
       <c r="F82">
-        <v>-0.6353993635648685</v>
+        <v>0.04628570975131743</v>
       </c>
       <c r="G82">
-        <v>-5.949975758463515</v>
+        <v>-3.085082152924264</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.319838746544828</v>
       </c>
       <c r="E83">
-        <v>-14.21350533068652</v>
+        <v>-10.72281718287997</v>
       </c>
       <c r="F83">
-        <v>-0.9092534850933711</v>
+        <v>0.244754255788051</v>
       </c>
       <c r="G83">
-        <v>-6.245781163269016</v>
+        <v>-3.415301009445221</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.449138093695231</v>
       </c>
       <c r="E84">
-        <v>-15.70978559840493</v>
+        <v>-11.20312977850353</v>
       </c>
       <c r="F84">
-        <v>-0.8568459929878576</v>
+        <v>0.1726597839876044</v>
       </c>
       <c r="G84">
-        <v>-6.431140650383607</v>
+        <v>-2.432023907169542</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.583178302888969</v>
       </c>
       <c r="E85">
-        <v>-16.54860389579373</v>
+        <v>-11.93749882290541</v>
       </c>
       <c r="F85">
-        <v>-1.081683130190505</v>
+        <v>0.1512498000948484</v>
       </c>
       <c r="G85">
-        <v>-5.920726949482625</v>
+        <v>-2.643357544148698</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.7225443559876</v>
       </c>
       <c r="E86">
-        <v>-17.47110386437026</v>
+        <v>-13.42086841122795</v>
       </c>
       <c r="F86">
-        <v>-0.8849740365173175</v>
+        <v>-0.3291279120952101</v>
       </c>
       <c r="G86">
-        <v>-5.736725888093644</v>
+        <v>-1.752883231238794</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.871569954768017</v>
       </c>
       <c r="E87">
-        <v>-18.71149365133724</v>
+        <v>-13.98393886934168</v>
       </c>
       <c r="F87">
-        <v>-1.057227239357655</v>
+        <v>-0.1817920007310816</v>
       </c>
       <c r="G87">
-        <v>-5.46871899233976</v>
+        <v>-3.100871391068313</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.031711043007824</v>
       </c>
       <c r="E88">
-        <v>-19.86616848228704</v>
+        <v>-15.83714892987066</v>
       </c>
       <c r="F88">
-        <v>-1.245243445505865</v>
+        <v>-0.01590065954424426</v>
       </c>
       <c r="G88">
-        <v>-5.488304603828085</v>
+        <v>-2.454953083426942</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.202551105410711</v>
       </c>
       <c r="E89">
-        <v>-21.25410500937193</v>
+        <v>-18.01634119184179</v>
       </c>
       <c r="F89">
-        <v>-1.60116558236452</v>
+        <v>-0.155794518161622</v>
       </c>
       <c r="G89">
-        <v>-5.101911234209434</v>
+        <v>-1.730928577784549</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.379824445415241</v>
       </c>
       <c r="E90">
-        <v>-22.82737386369475</v>
+        <v>-18.39487180566895</v>
       </c>
       <c r="F90">
-        <v>-1.288417126172372</v>
+        <v>0.1577218346129209</v>
       </c>
       <c r="G90">
-        <v>-5.747511263359539</v>
+        <v>-3.003579890609217</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.559948248378271</v>
       </c>
       <c r="E91">
-        <v>-24.57709923620044</v>
+        <v>-19.75451895562793</v>
       </c>
       <c r="F91">
-        <v>-1.510270483990136</v>
+        <v>-0.355571056327376</v>
       </c>
       <c r="G91">
-        <v>-5.256131928724896</v>
+        <v>-2.441381951057078</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-4.73410539908906</v>
       </c>
       <c r="E92">
-        <v>-26.58554085723835</v>
+        <v>-22.99086988926768</v>
       </c>
       <c r="F92">
-        <v>-1.645691158632396</v>
+        <v>-0.4518671101680128</v>
       </c>
       <c r="G92">
-        <v>-5.763149565311853</v>
+        <v>-2.099114448969841</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.891966864665523</v>
       </c>
       <c r="E93">
-        <v>-28.2379991365333</v>
+        <v>-24.9880446669745</v>
       </c>
       <c r="F93">
-        <v>-1.779191677634967</v>
+        <v>-0.4902909321468679</v>
       </c>
       <c r="G93">
-        <v>-5.219995835690731</v>
+        <v>-2.431968126403032</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-5.020086274532292</v>
       </c>
       <c r="E94">
-        <v>-30.3978095297516</v>
+        <v>-28.08188905206688</v>
       </c>
       <c r="F94">
-        <v>-1.827604782124181</v>
+        <v>-0.4347174198278547</v>
       </c>
       <c r="G94">
-        <v>-5.896304817415679</v>
+        <v>-2.446874715947589</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.110573487560693</v>
       </c>
       <c r="E95">
-        <v>-32.26770248852483</v>
+        <v>-31.0889180619582</v>
       </c>
       <c r="F95">
-        <v>-1.906998827478097</v>
+        <v>-0.9098664769714427</v>
       </c>
       <c r="G95">
-        <v>-5.633505220276632</v>
+        <v>-3.047781226236497</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.149744979282892</v>
       </c>
       <c r="E96">
-        <v>-34.35119677352887</v>
+        <v>-32.30739456320207</v>
       </c>
       <c r="F96">
-        <v>-2.06619861678512</v>
+        <v>-0.8117529850490637</v>
       </c>
       <c r="G96">
-        <v>-5.699493867058625</v>
+        <v>-2.665528758225866</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.135609594686127</v>
       </c>
       <c r="E97">
-        <v>-36.62790745901818</v>
+        <v>-34.82007044380905</v>
       </c>
       <c r="F97">
-        <v>-2.062350021831714</v>
+        <v>-1.151800289000469</v>
       </c>
       <c r="G97">
-        <v>-6.022398880723579</v>
+        <v>-3.231884005493821</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.052485913891982</v>
       </c>
       <c r="E98">
-        <v>-39.72247866418878</v>
+        <v>-37.09555617707928</v>
       </c>
       <c r="F98">
-        <v>-2.19109405520741</v>
+        <v>-1.021316684078894</v>
       </c>
       <c r="G98">
-        <v>-6.254374682533202</v>
+        <v>-2.569946774199241</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.916427976981957</v>
       </c>
       <c r="E99">
-        <v>-41.53869335631209</v>
+        <v>-40.92806939264382</v>
       </c>
       <c r="F99">
-        <v>-2.639245790326359</v>
+        <v>-1.427451967793047</v>
       </c>
       <c r="G99">
-        <v>-6.171340089749894</v>
+        <v>-3.811236171358737</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.702934665564254</v>
       </c>
       <c r="E100">
-        <v>-44.5708010552579</v>
+        <v>-42.30406206953348</v>
       </c>
       <c r="F100">
-        <v>-2.604260521436525</v>
+        <v>-1.31565384637642</v>
       </c>
       <c r="G100">
-        <v>-6.749415860428186</v>
+        <v>-3.912986851917117</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.450819642782816</v>
       </c>
       <c r="E101">
-        <v>-46.90175380241108</v>
+        <v>-45.38570900988619</v>
       </c>
       <c r="F101">
-        <v>-2.610313402048781</v>
+        <v>-1.77276271822184</v>
       </c>
       <c r="G101">
-        <v>-6.993167966414656</v>
+        <v>-4.193016143464808</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.094657881026599</v>
       </c>
       <c r="E102">
-        <v>-49.5951667412567</v>
+        <v>-48.83221962951092</v>
       </c>
       <c r="F102">
-        <v>-2.863997605686519</v>
+        <v>-1.853683444699116</v>
       </c>
       <c r="G102">
-        <v>-7.305474634442604</v>
+        <v>-3.527735347401154</v>
       </c>
     </row>
   </sheetData>
